--- a/artfynd/A 61096-2023 artfynd.xlsx
+++ b/artfynd/A 61096-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143034</v>
+        <v>121143033</v>
       </c>
       <c r="B2" t="n">
-        <v>8421</v>
+        <v>57502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477326</v>
+        <v>477493</v>
       </c>
       <c r="R2" t="n">
-        <v>6540800</v>
+        <v>6540743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,18 +761,12 @@
           <t>2023-10-04</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121143033</v>
+        <v>121143034</v>
       </c>
       <c r="B3" t="n">
-        <v>57499</v>
+        <v>8421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,35 +797,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477493</v>
+        <v>477326</v>
       </c>
       <c r="R3" t="n">
-        <v>6540743</v>
+        <v>6540800</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,12 +872,18 @@
           <t>2023-10-04</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61096-2023 artfynd.xlsx
+++ b/artfynd/A 61096-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121143033</v>
       </c>
       <c r="B2" t="n">
-        <v>57502</v>
+        <v>57505</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>121143034</v>
       </c>
       <c r="B3" t="n">
-        <v>8421</v>
+        <v>8424</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 61096-2023 artfynd.xlsx
+++ b/artfynd/A 61096-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143033</v>
+        <v>121143034</v>
       </c>
       <c r="B2" t="n">
-        <v>57505</v>
+        <v>8424</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477493</v>
+        <v>477326</v>
       </c>
       <c r="R2" t="n">
-        <v>6540743</v>
+        <v>6540800</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,12 +762,18 @@
           <t>2023-10-04</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121143034</v>
+        <v>121143033</v>
       </c>
       <c r="B3" t="n">
-        <v>8424</v>
+        <v>57505</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,36 +804,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477326</v>
+        <v>477493</v>
       </c>
       <c r="R3" t="n">
-        <v>6540800</v>
+        <v>6540743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,18 +878,12 @@
           <t>2023-10-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61096-2023 artfynd.xlsx
+++ b/artfynd/A 61096-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121143034</v>
+        <v>121143033</v>
       </c>
       <c r="B2" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477326</v>
+        <v>477493</v>
       </c>
       <c r="R2" t="n">
-        <v>6540800</v>
+        <v>6540743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,18 +756,12 @@
           <t>2023-10-04</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,47 +780,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121143033</v>
+        <v>121143034</v>
       </c>
       <c r="B3" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477493</v>
+        <v>477326</v>
       </c>
       <c r="R3" t="n">
-        <v>6540743</v>
+        <v>6540800</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,12 +862,18 @@
           <t>2023-10-04</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,6 +889,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122064957</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99646</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222541</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Borsttåg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Juncus squarrosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Laxån, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>477403</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6540879</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I mitten av sällan använd körväg.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Körväg genom hygge</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Weibull, Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Henriks bifångster</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61096-2023 artfynd.xlsx
+++ b/artfynd/A 61096-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143033</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143034</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,8 +1015,18 @@
           <t>Henriks bifångster</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122064957</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>